--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_24-04-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_24-04-2026.xlsx
@@ -523,17 +523,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -605,17 +605,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -687,17 +687,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -769,17 +769,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/eco-versal-2-4m-x-1-2m-all-sizes?variant=32222976245813</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1179,17 +1179,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1261,17 +1261,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1507,17 +1507,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1671,17 +1671,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
